--- a/artfynd/A 1959-2022 artfynd.xlsx
+++ b/artfynd/A 1959-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,2992 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120305419</v>
+      </c>
+      <c r="B3" t="n">
+        <v>94204</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2779</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Homalothecium sericeum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>483178</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7018955</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120304986</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>483067</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7019094</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120305078</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100171</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>483060</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7019069</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120304978</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>483102</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7019030</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120304937</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79475</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6441</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Slanklav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Collema flaccidum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>483123</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7019010</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120304923</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>483103</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7019023</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120305055</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78526</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>483137</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7019004</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120305317</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>483152</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7018936</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120304906</v>
+      </c>
+      <c r="B11" t="n">
+        <v>95455</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>53</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>483141</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7019037</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120305090</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100171</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>483055</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7019106</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120304940</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79475</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6441</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Slanklav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Collema flaccidum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>483147</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7019021</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120304910</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>483054</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7019113</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120304928</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79636</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>483101</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7019033</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120305013</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>483189</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7019015</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120304911</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>483181</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7019048</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120304920</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>483193</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7019005</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120305283</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96862</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>483154</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7018948</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120305096</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56514</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>483110</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7019046</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Läte</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120304987</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>483167</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7019007</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120305012</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>483208</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7019003</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120304927</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79636</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>483071</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7019044</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120304977</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>483111</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7019035</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120304916</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>483185</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7018955</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120305124</v>
+      </c>
+      <c r="B26" t="n">
+        <v>95455</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>53</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>483178</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7018954</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120305505</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>483156</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7018950</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120304957</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90846</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>658</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>483132</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7018969</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120304980</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>483130</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7019014</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120304976</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79607</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>483162</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7019011</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1959-2022 artfynd.xlsx
+++ b/artfynd/A 1959-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120272493</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120305419</v>
+        <v>120304911</v>
       </c>
       <c r="B3" t="n">
-        <v>94204</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483178</v>
+        <v>483181</v>
       </c>
       <c r="R3" t="n">
-        <v>7018955</v>
+        <v>7019048</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120304986</v>
+        <v>120304928</v>
       </c>
       <c r="B4" t="n">
-        <v>79607</v>
+        <v>79652</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483067</v>
+        <v>483101</v>
       </c>
       <c r="R4" t="n">
-        <v>7019094</v>
+        <v>7019033</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120305078</v>
+        <v>120305090</v>
       </c>
       <c r="B5" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483060</v>
+        <v>483055</v>
       </c>
       <c r="R5" t="n">
-        <v>7019069</v>
+        <v>7019106</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1112,7 @@
         <v>120304978</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120304937</v>
+        <v>120304923</v>
       </c>
       <c r="B7" t="n">
-        <v>79475</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6441</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483123</v>
+        <v>483103</v>
       </c>
       <c r="R7" t="n">
-        <v>7019010</v>
+        <v>7019023</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120304923</v>
+        <v>120304976</v>
       </c>
       <c r="B8" t="n">
-        <v>57463</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483103</v>
+        <v>483162</v>
       </c>
       <c r="R8" t="n">
-        <v>7019023</v>
+        <v>7019011</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120305055</v>
+        <v>120304986</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483137</v>
+        <v>483067</v>
       </c>
       <c r="R9" t="n">
-        <v>7019004</v>
+        <v>7019094</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120305317</v>
+        <v>120304980</v>
       </c>
       <c r="B10" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483152</v>
+        <v>483130</v>
       </c>
       <c r="R10" t="n">
-        <v>7018936</v>
+        <v>7019014</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120304906</v>
+        <v>120305078</v>
       </c>
       <c r="B11" t="n">
-        <v>95455</v>
+        <v>100194</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483141</v>
+        <v>483060</v>
       </c>
       <c r="R11" t="n">
-        <v>7019037</v>
+        <v>7019069</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120305090</v>
+        <v>120305013</v>
       </c>
       <c r="B12" t="n">
-        <v>100171</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1757,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483055</v>
+        <v>483189</v>
       </c>
       <c r="R12" t="n">
-        <v>7019106</v>
+        <v>7019015</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120304940</v>
+        <v>120304906</v>
       </c>
       <c r="B13" t="n">
-        <v>79475</v>
+        <v>95478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,25 +1863,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6441</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483147</v>
+        <v>483141</v>
       </c>
       <c r="R13" t="n">
-        <v>7019021</v>
+        <v>7019037</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120304910</v>
+        <v>120305317</v>
       </c>
       <c r="B14" t="n">
-        <v>90562</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483054</v>
+        <v>483152</v>
       </c>
       <c r="R14" t="n">
-        <v>7019113</v>
+        <v>7018936</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,12 +2031,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120304928</v>
+        <v>120304987</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2075,25 +2075,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483101</v>
+        <v>483167</v>
       </c>
       <c r="R15" t="n">
-        <v>7019033</v>
+        <v>7019007</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120305013</v>
+        <v>120304937</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>79491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,25 +2181,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6441</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483189</v>
+        <v>483123</v>
       </c>
       <c r="R16" t="n">
-        <v>7019015</v>
+        <v>7019010</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120304911</v>
+        <v>120305283</v>
       </c>
       <c r="B17" t="n">
-        <v>90562</v>
+        <v>96885</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,25 +2287,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483181</v>
+        <v>483154</v>
       </c>
       <c r="R17" t="n">
-        <v>7019048</v>
+        <v>7018948</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,12 +2349,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120304920</v>
+        <v>120305505</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2419,24 +2419,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483193</v>
+        <v>483156</v>
       </c>
       <c r="R18" t="n">
-        <v>7019005</v>
+        <v>7018950</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,12 +2455,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2495,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120305283</v>
+        <v>120304910</v>
       </c>
       <c r="B19" t="n">
-        <v>96862</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2507,25 +2504,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2539,10 +2536,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483154</v>
+        <v>483054</v>
       </c>
       <c r="R19" t="n">
-        <v>7018948</v>
+        <v>7019113</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,12 +2566,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120305096</v>
+        <v>120304940</v>
       </c>
       <c r="B20" t="n">
-        <v>56514</v>
+        <v>79491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2613,25 +2610,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>6441</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2645,10 +2642,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483110</v>
+        <v>483147</v>
       </c>
       <c r="R20" t="n">
-        <v>7019046</v>
+        <v>7019021</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,11 +2678,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120304987</v>
+        <v>120305419</v>
       </c>
       <c r="B21" t="n">
-        <v>79607</v>
+        <v>94227</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,25 +2716,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>2779</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2756,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483167</v>
+        <v>483178</v>
       </c>
       <c r="R21" t="n">
-        <v>7019007</v>
+        <v>7018955</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2786,12 +2778,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2818,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120305012</v>
+        <v>120305124</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>95478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2830,25 +2822,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2862,10 +2854,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483208</v>
+        <v>483178</v>
       </c>
       <c r="R22" t="n">
-        <v>7019003</v>
+        <v>7018954</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2892,12 +2884,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2924,10 +2916,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120304927</v>
+        <v>120304977</v>
       </c>
       <c r="B23" t="n">
-        <v>79636</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,25 +2928,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2968,10 +2960,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483071</v>
+        <v>483111</v>
       </c>
       <c r="R23" t="n">
-        <v>7019044</v>
+        <v>7019035</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3030,10 +3022,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120304977</v>
+        <v>120304927</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
+        <v>79652</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3042,25 +3034,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3074,10 +3066,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483111</v>
+        <v>483071</v>
       </c>
       <c r="R24" t="n">
-        <v>7019035</v>
+        <v>7019044</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120304916</v>
+        <v>120305096</v>
       </c>
       <c r="B25" t="n">
-        <v>90562</v>
+        <v>56524</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3152,21 +3144,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3180,10 +3172,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483185</v>
+        <v>483110</v>
       </c>
       <c r="R25" t="n">
-        <v>7018955</v>
+        <v>7019046</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,6 +3208,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3242,10 +3239,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120305124</v>
+        <v>120305012</v>
       </c>
       <c r="B26" t="n">
-        <v>95455</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3254,25 +3251,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3286,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483178</v>
+        <v>483208</v>
       </c>
       <c r="R26" t="n">
-        <v>7018954</v>
+        <v>7019003</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3316,12 +3313,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3348,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120305505</v>
+        <v>120304920</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3386,16 +3383,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483156</v>
+        <v>483193</v>
       </c>
       <c r="R27" t="n">
-        <v>7018950</v>
+        <v>7019005</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3422,17 +3427,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3459,10 +3459,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120304957</v>
+        <v>120305055</v>
       </c>
       <c r="B28" t="n">
-        <v>90846</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3475,21 +3475,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483132</v>
+        <v>483137</v>
       </c>
       <c r="R28" t="n">
-        <v>7018969</v>
+        <v>7019004</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3565,10 +3565,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120304980</v>
+        <v>120304916</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3581,21 +3581,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483130</v>
+        <v>483185</v>
       </c>
       <c r="R29" t="n">
-        <v>7019014</v>
+        <v>7018955</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120304976</v>
+        <v>120304957</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>90864</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3687,21 +3687,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483162</v>
+        <v>483132</v>
       </c>
       <c r="R30" t="n">
-        <v>7019011</v>
+        <v>7018969</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 1959-2022 artfynd.xlsx
+++ b/artfynd/A 1959-2022 artfynd.xlsx
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120305078</v>
+        <v>120304906</v>
       </c>
       <c r="B11" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483060</v>
+        <v>483141</v>
       </c>
       <c r="R11" t="n">
-        <v>7019069</v>
+        <v>7019037</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120305013</v>
+        <v>120305078</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1757,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483189</v>
+        <v>483060</v>
       </c>
       <c r="R12" t="n">
-        <v>7019015</v>
+        <v>7019069</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120304906</v>
+        <v>120305013</v>
       </c>
       <c r="B13" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,25 +1863,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483141</v>
+        <v>483189</v>
       </c>
       <c r="R13" t="n">
-        <v>7019037</v>
+        <v>7019015</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2598,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120304940</v>
+        <v>120305419</v>
       </c>
       <c r="B20" t="n">
-        <v>79491</v>
+        <v>94227</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2614,21 +2614,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6441</v>
+        <v>2779</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483147</v>
+        <v>483178</v>
       </c>
       <c r="R20" t="n">
-        <v>7019021</v>
+        <v>7018955</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2672,12 +2672,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120305419</v>
+        <v>120304940</v>
       </c>
       <c r="B21" t="n">
-        <v>94227</v>
+        <v>79491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2720,21 +2720,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2779</v>
+        <v>6441</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Slanklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Collema flaccidum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483178</v>
+        <v>483147</v>
       </c>
       <c r="R21" t="n">
-        <v>7018955</v>
+        <v>7019021</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 1959-2022 artfynd.xlsx
+++ b/artfynd/A 1959-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120304911</v>
+        <v>120304916</v>
       </c>
       <c r="B3" t="n">
         <v>90580</v>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483181</v>
+        <v>483185</v>
       </c>
       <c r="R3" t="n">
-        <v>7019048</v>
+        <v>7018955</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120304928</v>
+        <v>120305317</v>
       </c>
       <c r="B4" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483101</v>
+        <v>483152</v>
       </c>
       <c r="R4" t="n">
-        <v>7019033</v>
+        <v>7018936</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120305090</v>
+        <v>120304910</v>
       </c>
       <c r="B5" t="n">
-        <v>100194</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483055</v>
+        <v>483054</v>
       </c>
       <c r="R5" t="n">
-        <v>7019106</v>
+        <v>7019113</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120304978</v>
+        <v>120305055</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483102</v>
+        <v>483137</v>
       </c>
       <c r="R6" t="n">
-        <v>7019030</v>
+        <v>7019004</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120304923</v>
+        <v>120304978</v>
       </c>
       <c r="B7" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483103</v>
+        <v>483102</v>
       </c>
       <c r="R7" t="n">
-        <v>7019023</v>
+        <v>7019030</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,17 +1314,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120304976</v>
+        <v>120304920</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1359,16 +1359,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483162</v>
+        <v>483193</v>
       </c>
       <c r="R8" t="n">
-        <v>7019011</v>
+        <v>7019005</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,17 +1428,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120304986</v>
+        <v>120305283</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>96885</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1447,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1471,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483067</v>
+        <v>483154</v>
       </c>
       <c r="R9" t="n">
-        <v>7019094</v>
+        <v>7018948</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,12 +1509,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120304980</v>
+        <v>120305419</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>94227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1553,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2779</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1577,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483130</v>
+        <v>483178</v>
       </c>
       <c r="R10" t="n">
-        <v>7019014</v>
+        <v>7018955</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,12 +1615,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1851,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120305013</v>
+        <v>120305124</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,25 +1871,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483189</v>
+        <v>483178</v>
       </c>
       <c r="R13" t="n">
-        <v>7019015</v>
+        <v>7018954</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,12 +1933,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,7 +1965,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120305317</v>
+        <v>120304977</v>
       </c>
       <c r="B14" t="n">
         <v>79623</v>
@@ -2001,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483152</v>
+        <v>483111</v>
       </c>
       <c r="R14" t="n">
-        <v>7018936</v>
+        <v>7019035</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,12 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,17 +2064,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120304987</v>
+        <v>120304923</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,21 +2087,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2107,10 +2115,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483167</v>
+        <v>483103</v>
       </c>
       <c r="R15" t="n">
-        <v>7019007</v>
+        <v>7019023</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2162,17 +2170,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120304937</v>
+        <v>120305505</v>
       </c>
       <c r="B16" t="n">
-        <v>79491</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2181,25 +2189,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6441</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2213,10 +2221,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483123</v>
+        <v>483156</v>
       </c>
       <c r="R16" t="n">
-        <v>7019010</v>
+        <v>7018950</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,12 +2251,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,10 +2288,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120305283</v>
+        <v>120305090</v>
       </c>
       <c r="B17" t="n">
-        <v>96885</v>
+        <v>100194</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2304,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2319,10 +2332,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483154</v>
+        <v>483055</v>
       </c>
       <c r="R17" t="n">
-        <v>7018948</v>
+        <v>7019106</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,12 +2362,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,10 +2394,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120305505</v>
+        <v>120304927</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>79652</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,25 +2406,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2425,10 +2438,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483156</v>
+        <v>483071</v>
       </c>
       <c r="R18" t="n">
-        <v>7018950</v>
+        <v>7019044</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,17 +2468,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2485,17 +2493,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120304910</v>
+        <v>120304957</v>
       </c>
       <c r="B19" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,21 +2516,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2536,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483054</v>
+        <v>483132</v>
       </c>
       <c r="R19" t="n">
-        <v>7019113</v>
+        <v>7018969</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,17 +2599,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120305419</v>
+        <v>120304976</v>
       </c>
       <c r="B20" t="n">
-        <v>94227</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,25 +2618,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2779</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2642,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483178</v>
+        <v>483162</v>
       </c>
       <c r="R20" t="n">
-        <v>7018955</v>
+        <v>7019011</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2672,12 +2680,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2697,17 +2705,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120304940</v>
+        <v>120305096</v>
       </c>
       <c r="B21" t="n">
-        <v>79491</v>
+        <v>56524</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2716,25 +2724,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6441</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slanklav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Collema flaccidum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2748,10 +2756,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483147</v>
+        <v>483110</v>
       </c>
       <c r="R21" t="n">
-        <v>7019021</v>
+        <v>7019046</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,6 +2792,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,10 +2823,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120305124</v>
+        <v>120305013</v>
       </c>
       <c r="B22" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2822,25 +2835,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2854,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483178</v>
+        <v>483189</v>
       </c>
       <c r="R22" t="n">
-        <v>7018954</v>
+        <v>7019015</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2884,12 +2897,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2916,7 +2929,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120304977</v>
+        <v>120304987</v>
       </c>
       <c r="B23" t="n">
         <v>79623</v>
@@ -2960,10 +2973,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483111</v>
+        <v>483167</v>
       </c>
       <c r="R23" t="n">
-        <v>7019035</v>
+        <v>7019007</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,17 +3028,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120304927</v>
+        <v>120304980</v>
       </c>
       <c r="B24" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3034,25 +3047,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3066,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483071</v>
+        <v>483130</v>
       </c>
       <c r="R24" t="n">
-        <v>7019044</v>
+        <v>7019014</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,17 +3134,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120305096</v>
+        <v>120304911</v>
       </c>
       <c r="B25" t="n">
-        <v>56524</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3144,21 +3157,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3172,10 +3185,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483110</v>
+        <v>483181</v>
       </c>
       <c r="R25" t="n">
-        <v>7019046</v>
+        <v>7019048</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3208,11 +3221,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3239,10 +3247,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120305012</v>
+        <v>120304986</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3251,25 +3259,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3283,10 +3291,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483208</v>
+        <v>483067</v>
       </c>
       <c r="R26" t="n">
-        <v>7019003</v>
+        <v>7019094</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3338,17 +3346,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120304920</v>
+        <v>120304928</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>79652</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3357,25 +3365,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3383,24 +3391,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483193</v>
+        <v>483101</v>
       </c>
       <c r="R27" t="n">
-        <v>7019005</v>
+        <v>7019033</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3452,17 +3452,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305055</v>
+        <v>120305012</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3471,25 +3471,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483137</v>
+        <v>483208</v>
       </c>
       <c r="R28" t="n">
-        <v>7019004</v>
+        <v>7019003</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,218 +3562,6 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>120304916</v>
-      </c>
-      <c r="B29" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Kallkas, Jmt</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>483185</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7018955</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Ås</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Väg och Miljö AB</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>120304957</v>
-      </c>
-      <c r="B30" t="n">
-        <v>90864</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>658</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Kallkas, Jmt</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>483132</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7018969</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Ås</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Väg och Miljö AB</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1959-2022 artfynd.xlsx
+++ b/artfynd/A 1959-2022 artfynd.xlsx
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120304920</v>
+        <v>120305283</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>96885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1359,24 +1359,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483193</v>
+        <v>483154</v>
       </c>
       <c r="R8" t="n">
-        <v>7019005</v>
+        <v>7018948</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,12 +1395,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1428,17 +1420,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120305283</v>
+        <v>120304920</v>
       </c>
       <c r="B9" t="n">
-        <v>96885</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,25 +1439,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1473,16 +1465,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483154</v>
+        <v>483193</v>
       </c>
       <c r="R9" t="n">
-        <v>7018948</v>
+        <v>7019005</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 1959-2022 artfynd.xlsx
+++ b/artfynd/A 1959-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120304916</v>
+        <v>120304928</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>79652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483185</v>
+        <v>483101</v>
       </c>
       <c r="R3" t="n">
-        <v>7018955</v>
+        <v>7019033</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120305317</v>
+        <v>120304980</v>
       </c>
       <c r="B4" t="n">
         <v>79623</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483152</v>
+        <v>483130</v>
       </c>
       <c r="R4" t="n">
-        <v>7018936</v>
+        <v>7019014</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120304910</v>
+        <v>120305283</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>96885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483054</v>
+        <v>483154</v>
       </c>
       <c r="R5" t="n">
-        <v>7019113</v>
+        <v>7018948</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120305055</v>
+        <v>120305078</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>100194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483137</v>
+        <v>483060</v>
       </c>
       <c r="R6" t="n">
-        <v>7019004</v>
+        <v>7019069</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120304978</v>
+        <v>120304976</v>
       </c>
       <c r="B7" t="n">
         <v>79623</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483102</v>
+        <v>483162</v>
       </c>
       <c r="R7" t="n">
-        <v>7019030</v>
+        <v>7019011</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,17 +1314,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120305283</v>
+        <v>120305419</v>
       </c>
       <c r="B8" t="n">
-        <v>96885</v>
+        <v>94227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>2779</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483154</v>
+        <v>483178</v>
       </c>
       <c r="R8" t="n">
-        <v>7018948</v>
+        <v>7018955</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120304920</v>
+        <v>120304978</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1465,24 +1465,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483193</v>
+        <v>483102</v>
       </c>
       <c r="R9" t="n">
-        <v>7019005</v>
+        <v>7019030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,17 +1526,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120305419</v>
+        <v>120304910</v>
       </c>
       <c r="B10" t="n">
-        <v>94227</v>
+        <v>90580</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,25 +1545,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2779</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1585,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483178</v>
+        <v>483054</v>
       </c>
       <c r="R10" t="n">
-        <v>7018955</v>
+        <v>7019113</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,12 +1607,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120304906</v>
+        <v>120305013</v>
       </c>
       <c r="B11" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1691,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483141</v>
+        <v>483189</v>
       </c>
       <c r="R11" t="n">
-        <v>7019037</v>
+        <v>7019015</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120305078</v>
+        <v>120304927</v>
       </c>
       <c r="B12" t="n">
-        <v>100194</v>
+        <v>79652</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1797,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483060</v>
+        <v>483071</v>
       </c>
       <c r="R12" t="n">
-        <v>7019069</v>
+        <v>7019044</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120305124</v>
+        <v>120305055</v>
       </c>
       <c r="B13" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1875,21 +1867,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1903,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483178</v>
+        <v>483137</v>
       </c>
       <c r="R13" t="n">
-        <v>7018954</v>
+        <v>7019004</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,12 +1925,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120304977</v>
+        <v>120304957</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1981,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2009,10 +2001,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483111</v>
+        <v>483132</v>
       </c>
       <c r="R14" t="n">
-        <v>7019035</v>
+        <v>7018969</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,17 +2056,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120304923</v>
+        <v>120304986</v>
       </c>
       <c r="B15" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,21 +2079,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2115,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483103</v>
+        <v>483067</v>
       </c>
       <c r="R15" t="n">
-        <v>7019023</v>
+        <v>7019094</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,17 +2162,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120305505</v>
+        <v>120304977</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2193,21 +2185,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2221,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483156</v>
+        <v>483111</v>
       </c>
       <c r="R16" t="n">
-        <v>7018950</v>
+        <v>7019035</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,17 +2243,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2288,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120305090</v>
+        <v>120304920</v>
       </c>
       <c r="B17" t="n">
-        <v>100194</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2300,25 +2287,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2326,16 +2313,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483055</v>
+        <v>483193</v>
       </c>
       <c r="R17" t="n">
-        <v>7019106</v>
+        <v>7019005</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,10 +2389,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120304927</v>
+        <v>120304906</v>
       </c>
       <c r="B18" t="n">
-        <v>79652</v>
+        <v>95478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2406,25 +2401,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2438,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483071</v>
+        <v>483141</v>
       </c>
       <c r="R18" t="n">
-        <v>7019044</v>
+        <v>7019037</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,17 +2488,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120304957</v>
+        <v>120305505</v>
       </c>
       <c r="B19" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2516,21 +2511,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2544,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483132</v>
+        <v>483156</v>
       </c>
       <c r="R19" t="n">
-        <v>7018969</v>
+        <v>7018950</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,12 +2569,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,17 +2599,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120304976</v>
+        <v>120304911</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2622,21 +2622,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483162</v>
+        <v>483181</v>
       </c>
       <c r="R20" t="n">
-        <v>7019011</v>
+        <v>7019048</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,17 +2705,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120305096</v>
+        <v>120305124</v>
       </c>
       <c r="B21" t="n">
-        <v>56524</v>
+        <v>95478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483110</v>
+        <v>483178</v>
       </c>
       <c r="R21" t="n">
-        <v>7019046</v>
+        <v>7018954</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2786,17 +2786,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2823,10 +2818,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120305013</v>
+        <v>120305096</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>56524</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2835,25 +2830,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2867,10 +2862,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483189</v>
+        <v>483110</v>
       </c>
       <c r="R22" t="n">
-        <v>7019015</v>
+        <v>7019046</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2903,6 +2898,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120304980</v>
+        <v>120304923</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3051,21 +3051,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483130</v>
+        <v>483103</v>
       </c>
       <c r="R24" t="n">
-        <v>7019014</v>
+        <v>7019023</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,17 +3134,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120304911</v>
+        <v>120305012</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3153,25 +3153,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483181</v>
+        <v>483208</v>
       </c>
       <c r="R25" t="n">
-        <v>7019048</v>
+        <v>7019003</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3247,10 +3247,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120304986</v>
+        <v>120305090</v>
       </c>
       <c r="B26" t="n">
-        <v>79623</v>
+        <v>100194</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3259,25 +3259,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483067</v>
+        <v>483055</v>
       </c>
       <c r="R26" t="n">
-        <v>7019094</v>
+        <v>7019106</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3346,17 +3346,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120304928</v>
+        <v>120304916</v>
       </c>
       <c r="B27" t="n">
-        <v>79652</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3365,25 +3365,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483101</v>
+        <v>483185</v>
       </c>
       <c r="R27" t="n">
-        <v>7019033</v>
+        <v>7018955</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3452,17 +3452,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305012</v>
+        <v>120305317</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3471,25 +3471,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483208</v>
+        <v>483152</v>
       </c>
       <c r="R28" t="n">
-        <v>7019003</v>
+        <v>7018936</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3533,12 +3533,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 1959-2022 artfynd.xlsx
+++ b/artfynd/A 1959-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120304928</v>
+        <v>120304910</v>
       </c>
       <c r="B3" t="n">
-        <v>79652</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483101</v>
+        <v>483054</v>
       </c>
       <c r="R3" t="n">
-        <v>7019033</v>
+        <v>7019113</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120304980</v>
+        <v>120304987</v>
       </c>
       <c r="B4" t="n">
         <v>79623</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483130</v>
+        <v>483167</v>
       </c>
       <c r="R4" t="n">
-        <v>7019014</v>
+        <v>7019007</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120305283</v>
+        <v>120304976</v>
       </c>
       <c r="B5" t="n">
-        <v>96885</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483154</v>
+        <v>483162</v>
       </c>
       <c r="R5" t="n">
-        <v>7018948</v>
+        <v>7019011</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120305078</v>
+        <v>120305317</v>
       </c>
       <c r="B6" t="n">
-        <v>100194</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483060</v>
+        <v>483152</v>
       </c>
       <c r="R6" t="n">
-        <v>7019069</v>
+        <v>7018936</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120304976</v>
+        <v>120304977</v>
       </c>
       <c r="B7" t="n">
         <v>79623</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483162</v>
+        <v>483111</v>
       </c>
       <c r="R7" t="n">
-        <v>7019011</v>
+        <v>7019035</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120305419</v>
+        <v>120304980</v>
       </c>
       <c r="B8" t="n">
-        <v>94227</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2779</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483178</v>
+        <v>483130</v>
       </c>
       <c r="R8" t="n">
-        <v>7018955</v>
+        <v>7019014</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120304978</v>
+        <v>120305078</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>100194</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1439,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483102</v>
+        <v>483060</v>
       </c>
       <c r="R9" t="n">
-        <v>7019030</v>
+        <v>7019069</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,17 +1526,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120304910</v>
+        <v>120304957</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483054</v>
+        <v>483132</v>
       </c>
       <c r="R10" t="n">
-        <v>7019113</v>
+        <v>7018969</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120305013</v>
+        <v>120305012</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483189</v>
+        <v>483208</v>
       </c>
       <c r="R11" t="n">
-        <v>7019015</v>
+        <v>7019003</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120304927</v>
+        <v>120304906</v>
       </c>
       <c r="B12" t="n">
-        <v>79652</v>
+        <v>95478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1757,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483071</v>
+        <v>483141</v>
       </c>
       <c r="R12" t="n">
-        <v>7019044</v>
+        <v>7019037</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120305055</v>
+        <v>120305419</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>94227</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,25 +1863,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2779</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483137</v>
+        <v>483178</v>
       </c>
       <c r="R13" t="n">
-        <v>7019004</v>
+        <v>7018955</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120304957</v>
+        <v>120305505</v>
       </c>
       <c r="B14" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,21 +1973,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483132</v>
+        <v>483156</v>
       </c>
       <c r="R14" t="n">
-        <v>7018969</v>
+        <v>7018950</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,12 +2031,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120304986</v>
+        <v>120304911</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2079,21 +2084,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2107,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483067</v>
+        <v>483181</v>
       </c>
       <c r="R15" t="n">
-        <v>7019094</v>
+        <v>7019048</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120304977</v>
+        <v>120305055</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,21 +2190,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2213,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483111</v>
+        <v>483137</v>
       </c>
       <c r="R16" t="n">
-        <v>7019035</v>
+        <v>7019004</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120304920</v>
+        <v>120304928</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>79652</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2287,25 +2292,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2313,24 +2318,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483193</v>
+        <v>483101</v>
       </c>
       <c r="R17" t="n">
-        <v>7019005</v>
+        <v>7019033</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120304906</v>
+        <v>120304916</v>
       </c>
       <c r="B18" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2405,21 +2402,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2433,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483141</v>
+        <v>483185</v>
       </c>
       <c r="R18" t="n">
-        <v>7019037</v>
+        <v>7018955</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2495,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120305505</v>
+        <v>120305096</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>56524</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2511,16 +2508,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2539,10 +2536,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483156</v>
+        <v>483110</v>
       </c>
       <c r="R19" t="n">
-        <v>7018950</v>
+        <v>7019046</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,17 +2566,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,17 +2596,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120304911</v>
+        <v>120305090</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>100194</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2618,25 +2615,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2650,10 +2647,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483181</v>
+        <v>483055</v>
       </c>
       <c r="R20" t="n">
-        <v>7019048</v>
+        <v>7019106</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,7 +2702,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2811,17 +2808,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120305096</v>
+        <v>120304978</v>
       </c>
       <c r="B22" t="n">
-        <v>56524</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2834,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2862,10 +2859,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483110</v>
+        <v>483102</v>
       </c>
       <c r="R22" t="n">
-        <v>7019046</v>
+        <v>7019030</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2898,11 +2895,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2929,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120304987</v>
+        <v>120305283</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>96885</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2941,25 +2933,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2973,10 +2965,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483167</v>
+        <v>483154</v>
       </c>
       <c r="R23" t="n">
-        <v>7019007</v>
+        <v>7018948</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3003,12 +2995,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3141,7 +3133,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120305012</v>
+        <v>120305013</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3185,10 +3177,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483208</v>
+        <v>483189</v>
       </c>
       <c r="R25" t="n">
-        <v>7019003</v>
+        <v>7019015</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3247,10 +3239,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120305090</v>
+        <v>120304986</v>
       </c>
       <c r="B26" t="n">
-        <v>100194</v>
+        <v>79623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3259,25 +3251,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3291,10 +3283,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483055</v>
+        <v>483067</v>
       </c>
       <c r="R26" t="n">
-        <v>7019106</v>
+        <v>7019094</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3353,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120304916</v>
+        <v>120304927</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>79652</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3365,25 +3357,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3397,10 +3389,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483185</v>
+        <v>483071</v>
       </c>
       <c r="R27" t="n">
-        <v>7018955</v>
+        <v>7019044</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3459,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305317</v>
+        <v>120304920</v>
       </c>
       <c r="B28" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3475,21 +3467,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3497,16 +3489,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483152</v>
+        <v>483193</v>
       </c>
       <c r="R28" t="n">
-        <v>7018936</v>
+        <v>7019005</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3533,12 +3533,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 1959-2022 artfynd.xlsx
+++ b/artfynd/A 1959-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120304910</v>
+        <v>120305124</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483054</v>
+        <v>483178</v>
       </c>
       <c r="R3" t="n">
-        <v>7019113</v>
+        <v>7018954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,14 +890,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120304987</v>
+        <v>120304986</v>
       </c>
       <c r="B4" t="n">
         <v>79623</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483167</v>
+        <v>483067</v>
       </c>
       <c r="R4" t="n">
-        <v>7019007</v>
+        <v>7019094</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120304976</v>
+        <v>120305317</v>
       </c>
       <c r="B5" t="n">
         <v>79623</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483162</v>
+        <v>483152</v>
       </c>
       <c r="R5" t="n">
-        <v>7019011</v>
+        <v>7018936</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120305317</v>
+        <v>120305096</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>56524</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483152</v>
+        <v>483110</v>
       </c>
       <c r="R6" t="n">
-        <v>7018936</v>
+        <v>7019046</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,12 +1183,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,17 +1213,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120304977</v>
+        <v>120304916</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483111</v>
+        <v>483185</v>
       </c>
       <c r="R7" t="n">
-        <v>7019035</v>
+        <v>7018955</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120304980</v>
+        <v>120304911</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1342,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1365,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483130</v>
+        <v>483181</v>
       </c>
       <c r="R8" t="n">
-        <v>7019014</v>
+        <v>7019048</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120305078</v>
+        <v>120304928</v>
       </c>
       <c r="B9" t="n">
-        <v>100194</v>
+        <v>79652</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1448,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1471,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483060</v>
+        <v>483101</v>
       </c>
       <c r="R9" t="n">
-        <v>7019069</v>
+        <v>7019033</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,17 +1531,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120304957</v>
+        <v>120304980</v>
       </c>
       <c r="B10" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1554,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1577,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483132</v>
+        <v>483130</v>
       </c>
       <c r="R10" t="n">
-        <v>7018969</v>
+        <v>7019014</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1639,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120305012</v>
+        <v>120304920</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1656,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1677,16 +1682,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483208</v>
+        <v>483193</v>
       </c>
       <c r="R11" t="n">
-        <v>7019003</v>
+        <v>7019005</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120304906</v>
+        <v>120305283</v>
       </c>
       <c r="B12" t="n">
-        <v>95478</v>
+        <v>96885</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1770,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483141</v>
+        <v>483154</v>
       </c>
       <c r="R12" t="n">
-        <v>7019037</v>
+        <v>7018948</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,12 +1832,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,10 +1864,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120305419</v>
+        <v>120304910</v>
       </c>
       <c r="B13" t="n">
-        <v>94227</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,25 +1876,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2779</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,10 +1908,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483178</v>
+        <v>483054</v>
       </c>
       <c r="R13" t="n">
-        <v>7018955</v>
+        <v>7019113</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,12 +1938,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120305505</v>
+        <v>120304977</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483156</v>
+        <v>483111</v>
       </c>
       <c r="R14" t="n">
-        <v>7018950</v>
+        <v>7019035</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,17 +2044,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2068,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120304911</v>
+        <v>120305055</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2084,21 +2092,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2112,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483181</v>
+        <v>483137</v>
       </c>
       <c r="R15" t="n">
-        <v>7019048</v>
+        <v>7019004</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2174,10 +2182,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120305055</v>
+        <v>120305505</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2190,21 +2198,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2218,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483137</v>
+        <v>483156</v>
       </c>
       <c r="R16" t="n">
-        <v>7019004</v>
+        <v>7018950</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,12 +2256,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120304928</v>
+        <v>120304987</v>
       </c>
       <c r="B17" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2292,25 +2305,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2324,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483101</v>
+        <v>483167</v>
       </c>
       <c r="R17" t="n">
-        <v>7019033</v>
+        <v>7019007</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,10 +2399,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120304916</v>
+        <v>120304957</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2402,21 +2415,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2430,10 +2443,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483185</v>
+        <v>483132</v>
       </c>
       <c r="R18" t="n">
-        <v>7018955</v>
+        <v>7018969</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,10 +2505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120305096</v>
+        <v>120305090</v>
       </c>
       <c r="B19" t="n">
-        <v>56524</v>
+        <v>100194</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,25 +2517,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2536,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483110</v>
+        <v>483055</v>
       </c>
       <c r="R19" t="n">
-        <v>7019046</v>
+        <v>7019106</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2572,11 +2585,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120305090</v>
+        <v>120304906</v>
       </c>
       <c r="B20" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,25 +2623,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2647,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483055</v>
+        <v>483141</v>
       </c>
       <c r="R20" t="n">
-        <v>7019106</v>
+        <v>7019037</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2702,17 +2710,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120305124</v>
+        <v>120304923</v>
       </c>
       <c r="B21" t="n">
-        <v>95478</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2725,21 +2733,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2753,10 +2761,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483178</v>
+        <v>483103</v>
       </c>
       <c r="R21" t="n">
-        <v>7018954</v>
+        <v>7019023</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,12 +2791,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2808,17 +2816,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120304978</v>
+        <v>120305013</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2827,25 +2835,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2859,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483102</v>
+        <v>483189</v>
       </c>
       <c r="R22" t="n">
-        <v>7019030</v>
+        <v>7019015</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2921,10 +2929,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120305283</v>
+        <v>120304927</v>
       </c>
       <c r="B23" t="n">
-        <v>96885</v>
+        <v>79652</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2937,21 +2945,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2965,10 +2973,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483154</v>
+        <v>483071</v>
       </c>
       <c r="R23" t="n">
-        <v>7018948</v>
+        <v>7019044</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2995,12 +3003,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120304923</v>
+        <v>120304978</v>
       </c>
       <c r="B24" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3043,21 +3051,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3071,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483103</v>
+        <v>483102</v>
       </c>
       <c r="R24" t="n">
-        <v>7019023</v>
+        <v>7019030</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3133,10 +3141,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120305013</v>
+        <v>120304976</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3145,25 +3153,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3177,10 +3185,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483189</v>
+        <v>483162</v>
       </c>
       <c r="R25" t="n">
-        <v>7019015</v>
+        <v>7019011</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3239,10 +3247,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120304986</v>
+        <v>120305419</v>
       </c>
       <c r="B26" t="n">
-        <v>79623</v>
+        <v>94227</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3251,25 +3259,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>2779</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3283,10 +3291,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483067</v>
+        <v>483178</v>
       </c>
       <c r="R26" t="n">
-        <v>7019094</v>
+        <v>7018955</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,12 +3321,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,10 +3353,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120304927</v>
+        <v>120305078</v>
       </c>
       <c r="B27" t="n">
-        <v>79652</v>
+        <v>100194</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3361,21 +3369,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3389,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483071</v>
+        <v>483060</v>
       </c>
       <c r="R27" t="n">
-        <v>7019044</v>
+        <v>7019069</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3444,17 +3452,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120304920</v>
+        <v>120305012</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3463,25 +3471,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3489,24 +3497,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483193</v>
+        <v>483208</v>
       </c>
       <c r="R28" t="n">
-        <v>7019005</v>
+        <v>7019003</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 1959-2022 artfynd.xlsx
+++ b/artfynd/A 1959-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120305124</v>
+        <v>120305096</v>
       </c>
       <c r="B3" t="n">
-        <v>95478</v>
+        <v>56524</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483178</v>
+        <v>483110</v>
       </c>
       <c r="R3" t="n">
-        <v>7018954</v>
+        <v>7019046</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +865,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120304986</v>
+        <v>120305124</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>95478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +918,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483067</v>
+        <v>483178</v>
       </c>
       <c r="R4" t="n">
-        <v>7019094</v>
+        <v>7018954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,14 +1001,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120305317</v>
+        <v>120304986</v>
       </c>
       <c r="B5" t="n">
         <v>79623</v>
@@ -1047,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483152</v>
+        <v>483067</v>
       </c>
       <c r="R5" t="n">
-        <v>7018936</v>
+        <v>7019094</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120305096</v>
+        <v>120305317</v>
       </c>
       <c r="B6" t="n">
-        <v>56524</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1153,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483110</v>
+        <v>483152</v>
       </c>
       <c r="R6" t="n">
-        <v>7019046</v>
+        <v>7018936</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,17 +1188,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120305055</v>
+        <v>120305505</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2092,21 +2092,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483137</v>
+        <v>483156</v>
       </c>
       <c r="R15" t="n">
-        <v>7019004</v>
+        <v>7018950</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,12 +2150,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120305505</v>
+        <v>120305055</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2198,21 +2203,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2226,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483156</v>
+        <v>483137</v>
       </c>
       <c r="R16" t="n">
-        <v>7018950</v>
+        <v>7019004</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,17 +2261,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 1959-2022 artfynd.xlsx
+++ b/artfynd/A 1959-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120305096</v>
+        <v>120305419</v>
       </c>
       <c r="B3" t="n">
-        <v>56524</v>
+        <v>94227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483110</v>
+        <v>483178</v>
       </c>
       <c r="R3" t="n">
-        <v>7019046</v>
+        <v>7018955</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,17 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,17 +890,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120305124</v>
+        <v>120305078</v>
       </c>
       <c r="B4" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -946,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483178</v>
+        <v>483060</v>
       </c>
       <c r="R4" t="n">
-        <v>7018954</v>
+        <v>7019069</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,17 +996,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120304986</v>
+        <v>120304957</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483067</v>
+        <v>483132</v>
       </c>
       <c r="R5" t="n">
-        <v>7019094</v>
+        <v>7018969</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120305317</v>
+        <v>120304920</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1152,16 +1147,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483152</v>
+        <v>483193</v>
       </c>
       <c r="R6" t="n">
-        <v>7018936</v>
+        <v>7019005</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,12 +1191,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120304916</v>
+        <v>120304923</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,21 +1239,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1264,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483185</v>
+        <v>483103</v>
       </c>
       <c r="R7" t="n">
-        <v>7018955</v>
+        <v>7019023</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120304911</v>
+        <v>120305096</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>56524</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,21 +1345,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1370,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483181</v>
+        <v>483110</v>
       </c>
       <c r="R8" t="n">
-        <v>7019048</v>
+        <v>7019046</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,6 +1409,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120304928</v>
+        <v>120304916</v>
       </c>
       <c r="B9" t="n">
-        <v>79652</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,25 +1452,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1476,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483101</v>
+        <v>483185</v>
       </c>
       <c r="R9" t="n">
-        <v>7019033</v>
+        <v>7018955</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,10 +1546,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120304980</v>
+        <v>120305505</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,21 +1562,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1582,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483130</v>
+        <v>483156</v>
       </c>
       <c r="R10" t="n">
-        <v>7019014</v>
+        <v>7018950</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,12 +1620,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,10 +1657,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120304920</v>
+        <v>120304986</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,21 +1673,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1682,24 +1695,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483193</v>
+        <v>483067</v>
       </c>
       <c r="R11" t="n">
-        <v>7019005</v>
+        <v>7019094</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120305283</v>
+        <v>120304980</v>
       </c>
       <c r="B12" t="n">
-        <v>96885</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,25 +1775,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1802,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483154</v>
+        <v>483130</v>
       </c>
       <c r="R12" t="n">
-        <v>7018948</v>
+        <v>7019014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,12 +1837,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120304910</v>
+        <v>120304977</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,21 +1885,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1908,10 +1913,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483054</v>
+        <v>483111</v>
       </c>
       <c r="R13" t="n">
-        <v>7019113</v>
+        <v>7019035</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1970,7 +1975,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120304977</v>
+        <v>120305317</v>
       </c>
       <c r="B14" t="n">
         <v>79623</v>
@@ -2014,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483111</v>
+        <v>483152</v>
       </c>
       <c r="R14" t="n">
-        <v>7019035</v>
+        <v>7018936</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,12 +2049,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120305505</v>
+        <v>120305124</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>95478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2092,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2120,10 +2125,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483156</v>
+        <v>483178</v>
       </c>
       <c r="R15" t="n">
-        <v>7018950</v>
+        <v>7018954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,11 +2161,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120305055</v>
+        <v>120304910</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,21 +2203,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483137</v>
+        <v>483054</v>
       </c>
       <c r="R16" t="n">
-        <v>7019004</v>
+        <v>7019113</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120304987</v>
+        <v>120305012</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,25 +2305,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483167</v>
+        <v>483208</v>
       </c>
       <c r="R17" t="n">
-        <v>7019007</v>
+        <v>7019003</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120304957</v>
+        <v>120304978</v>
       </c>
       <c r="B18" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2415,21 +2415,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483132</v>
+        <v>483102</v>
       </c>
       <c r="R18" t="n">
-        <v>7018969</v>
+        <v>7019030</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120305090</v>
+        <v>120304987</v>
       </c>
       <c r="B19" t="n">
-        <v>100194</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2517,25 +2517,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483055</v>
+        <v>483167</v>
       </c>
       <c r="R19" t="n">
-        <v>7019106</v>
+        <v>7019007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2604,17 +2604,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120304906</v>
+        <v>120305055</v>
       </c>
       <c r="B20" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,21 +2627,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483141</v>
+        <v>483137</v>
       </c>
       <c r="R20" t="n">
-        <v>7019037</v>
+        <v>7019004</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120304923</v>
+        <v>120304906</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>95478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483103</v>
+        <v>483141</v>
       </c>
       <c r="R21" t="n">
-        <v>7019023</v>
+        <v>7019037</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120305013</v>
+        <v>120304976</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2835,25 +2835,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483189</v>
+        <v>483162</v>
       </c>
       <c r="R22" t="n">
-        <v>7019015</v>
+        <v>7019011</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3035,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120304978</v>
+        <v>120304928</v>
       </c>
       <c r="B24" t="n">
-        <v>79623</v>
+        <v>79652</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3047,25 +3047,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483102</v>
+        <v>483101</v>
       </c>
       <c r="R24" t="n">
-        <v>7019030</v>
+        <v>7019033</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,10 +3141,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120304976</v>
+        <v>120305013</v>
       </c>
       <c r="B25" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3153,25 +3153,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483162</v>
+        <v>483189</v>
       </c>
       <c r="R25" t="n">
-        <v>7019011</v>
+        <v>7019015</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3247,10 +3247,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120305419</v>
+        <v>120305090</v>
       </c>
       <c r="B26" t="n">
-        <v>94227</v>
+        <v>100194</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3263,21 +3263,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2779</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483178</v>
+        <v>483055</v>
       </c>
       <c r="R26" t="n">
-        <v>7018955</v>
+        <v>7019106</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3321,12 +3321,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3353,10 +3353,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120305078</v>
+        <v>120304911</v>
       </c>
       <c r="B27" t="n">
-        <v>100194</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3365,25 +3365,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483060</v>
+        <v>483181</v>
       </c>
       <c r="R27" t="n">
-        <v>7019069</v>
+        <v>7019048</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3452,17 +3452,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305012</v>
+        <v>120305283</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3471,25 +3471,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483208</v>
+        <v>483154</v>
       </c>
       <c r="R28" t="n">
-        <v>7019003</v>
+        <v>7018948</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3533,12 +3533,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 1959-2022 artfynd.xlsx
+++ b/artfynd/A 1959-2022 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120305419</v>
+        <v>120304906</v>
       </c>
       <c r="B3" t="n">
-        <v>94227</v>
+        <v>95478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483178</v>
+        <v>483141</v>
       </c>
       <c r="R3" t="n">
-        <v>7018955</v>
+        <v>7019037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120305078</v>
+        <v>120304910</v>
       </c>
       <c r="B4" t="n">
-        <v>100194</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483060</v>
+        <v>483054</v>
       </c>
       <c r="R4" t="n">
-        <v>7019069</v>
+        <v>7019113</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120304957</v>
+        <v>120304927</v>
       </c>
       <c r="B5" t="n">
-        <v>90864</v>
+        <v>79652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483132</v>
+        <v>483071</v>
       </c>
       <c r="R5" t="n">
-        <v>7018969</v>
+        <v>7019044</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120304920</v>
+        <v>120305012</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1147,24 +1147,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483193</v>
+        <v>483208</v>
       </c>
       <c r="R6" t="n">
-        <v>7019005</v>
+        <v>7019003</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120304923</v>
+        <v>120305013</v>
       </c>
       <c r="B7" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1267,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483103</v>
+        <v>483189</v>
       </c>
       <c r="R7" t="n">
-        <v>7019023</v>
+        <v>7019015</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120305096</v>
+        <v>120304916</v>
       </c>
       <c r="B8" t="n">
-        <v>56524</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1373,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483110</v>
+        <v>483185</v>
       </c>
       <c r="R8" t="n">
-        <v>7019046</v>
+        <v>7018955</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,11 +1401,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Läte</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120304916</v>
+        <v>120304986</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1484,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483185</v>
+        <v>483067</v>
       </c>
       <c r="R9" t="n">
-        <v>7018955</v>
+        <v>7019094</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120305505</v>
+        <v>120304923</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,21 +1549,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1590,10 +1577,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483156</v>
+        <v>483103</v>
       </c>
       <c r="R10" t="n">
-        <v>7018950</v>
+        <v>7019023</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,17 +1607,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,7 +1639,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120304986</v>
+        <v>120305317</v>
       </c>
       <c r="B11" t="n">
         <v>79623</v>
@@ -1701,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483067</v>
+        <v>483152</v>
       </c>
       <c r="R11" t="n">
-        <v>7019094</v>
+        <v>7018936</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,12 +1713,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120304980</v>
+        <v>120305078</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>100194</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,25 +1757,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1807,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483130</v>
+        <v>483060</v>
       </c>
       <c r="R12" t="n">
-        <v>7019014</v>
+        <v>7019069</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120304977</v>
+        <v>120304957</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,21 +1867,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1913,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483111</v>
+        <v>483132</v>
       </c>
       <c r="R13" t="n">
-        <v>7019035</v>
+        <v>7018969</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,7 +1957,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120305317</v>
+        <v>120304977</v>
       </c>
       <c r="B14" t="n">
         <v>79623</v>
@@ -2019,10 +2001,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483152</v>
+        <v>483111</v>
       </c>
       <c r="R14" t="n">
-        <v>7018936</v>
+        <v>7019035</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,12 +2031,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120305124</v>
+        <v>120304980</v>
       </c>
       <c r="B15" t="n">
-        <v>95478</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,21 +2079,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2125,10 +2107,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483178</v>
+        <v>483130</v>
       </c>
       <c r="R15" t="n">
-        <v>7018954</v>
+        <v>7019014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2155,12 +2137,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2187,7 +2169,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120304910</v>
+        <v>120304911</v>
       </c>
       <c r="B16" t="n">
         <v>90580</v>
@@ -2231,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483054</v>
+        <v>483181</v>
       </c>
       <c r="R16" t="n">
-        <v>7019113</v>
+        <v>7019048</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120305012</v>
+        <v>120304920</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,25 +2287,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2331,16 +2313,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483208</v>
+        <v>483193</v>
       </c>
       <c r="R17" t="n">
-        <v>7019003</v>
+        <v>7019005</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2399,10 +2389,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120304978</v>
+        <v>120305090</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>100194</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,25 +2401,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2443,10 +2433,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483102</v>
+        <v>483055</v>
       </c>
       <c r="R18" t="n">
-        <v>7019030</v>
+        <v>7019106</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2505,7 +2495,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120304987</v>
+        <v>120304978</v>
       </c>
       <c r="B19" t="n">
         <v>79623</v>
@@ -2549,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483167</v>
+        <v>483102</v>
       </c>
       <c r="R19" t="n">
-        <v>7019007</v>
+        <v>7019030</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120305055</v>
+        <v>120305096</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>56524</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,21 +2617,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2655,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483137</v>
+        <v>483110</v>
       </c>
       <c r="R20" t="n">
-        <v>7019004</v>
+        <v>7019046</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,6 +2681,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2717,7 +2712,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120304906</v>
+        <v>120305124</v>
       </c>
       <c r="B21" t="n">
         <v>95478</v>
@@ -2761,10 +2756,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483141</v>
+        <v>483178</v>
       </c>
       <c r="R21" t="n">
-        <v>7019037</v>
+        <v>7018954</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2791,12 +2786,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2929,10 +2924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120304927</v>
+        <v>120305055</v>
       </c>
       <c r="B23" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2941,25 +2936,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2973,10 +2968,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483071</v>
+        <v>483137</v>
       </c>
       <c r="R23" t="n">
-        <v>7019044</v>
+        <v>7019004</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3035,10 +3030,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120304928</v>
+        <v>120304987</v>
       </c>
       <c r="B24" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3047,25 +3042,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3079,10 +3074,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483101</v>
+        <v>483167</v>
       </c>
       <c r="R24" t="n">
-        <v>7019033</v>
+        <v>7019007</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3141,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120305013</v>
+        <v>120305505</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3153,25 +3148,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3185,10 +3180,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483189</v>
+        <v>483156</v>
       </c>
       <c r="R25" t="n">
-        <v>7019015</v>
+        <v>7018950</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3215,12 +3210,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3247,10 +3247,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120305090</v>
+        <v>120305283</v>
       </c>
       <c r="B26" t="n">
-        <v>100194</v>
+        <v>96885</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3263,21 +3263,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483055</v>
+        <v>483154</v>
       </c>
       <c r="R26" t="n">
-        <v>7019106</v>
+        <v>7018948</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3321,12 +3321,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3353,10 +3353,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120304911</v>
+        <v>120305419</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>94227</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3365,25 +3365,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>2779</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483181</v>
+        <v>483178</v>
       </c>
       <c r="R27" t="n">
-        <v>7019048</v>
+        <v>7018955</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3427,12 +3427,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3459,10 +3459,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305283</v>
+        <v>120304928</v>
       </c>
       <c r="B28" t="n">
-        <v>96885</v>
+        <v>79652</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3475,21 +3475,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483154</v>
+        <v>483101</v>
       </c>
       <c r="R28" t="n">
-        <v>7018948</v>
+        <v>7019033</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3533,12 +3533,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 1959-2022 artfynd.xlsx
+++ b/artfynd/A 1959-2022 artfynd.xlsx
@@ -1639,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120305317</v>
+        <v>120305078</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>100194</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483152</v>
+        <v>483060</v>
       </c>
       <c r="R11" t="n">
-        <v>7018936</v>
+        <v>7019069</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,12 +1713,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120305078</v>
+        <v>120305317</v>
       </c>
       <c r="B12" t="n">
-        <v>100194</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1757,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483060</v>
+        <v>483152</v>
       </c>
       <c r="R12" t="n">
-        <v>7019069</v>
+        <v>7018936</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,12 +1819,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 1959-2022 artfynd.xlsx
+++ b/artfynd/A 1959-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120272493</v>
+        <v>120304905</v>
       </c>
       <c r="B2" t="n">
-        <v>57485</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,48 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sveden, Sveden, Jmt</t>
+          <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483195</v>
+        <v>483225</v>
       </c>
       <c r="R2" t="n">
-        <v>7018972</v>
+        <v>7018988</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +764,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120304910</v>
+        <v>120304906</v>
       </c>
       <c r="B3" t="n">
-        <v>90636</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483054</v>
+        <v>483141</v>
       </c>
       <c r="R3" t="n">
-        <v>7019113</v>
+        <v>7019037</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120305283</v>
+        <v>120305124</v>
       </c>
       <c r="B4" t="n">
-        <v>96960</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483154</v>
+        <v>483178</v>
       </c>
       <c r="R4" t="n">
-        <v>7018948</v>
+        <v>7018954</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,22 +971,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120305317</v>
+        <v>120420881</v>
       </c>
       <c r="B5" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1043,14 +1013,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kallkas, Jmt</t>
+          <t>kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483152</v>
+        <v>483207</v>
       </c>
       <c r="R5" t="n">
-        <v>7018936</v>
+        <v>7018964</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,12 +1047,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,22 +1072,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120304987</v>
+        <v>120304957</v>
       </c>
       <c r="B6" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1153,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483167</v>
+        <v>483132</v>
       </c>
       <c r="R6" t="n">
-        <v>7019007</v>
+        <v>7018969</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120304978</v>
+        <v>120305407</v>
       </c>
       <c r="B7" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483102</v>
+        <v>483210</v>
       </c>
       <c r="R7" t="n">
-        <v>7019030</v>
+        <v>7018958</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,12 +1249,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120305419</v>
+        <v>120420884</v>
       </c>
       <c r="B8" t="n">
-        <v>94302</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2779</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1361,14 +1316,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kallkas, Jmt</t>
+          <t>kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483178</v>
+        <v>483182</v>
       </c>
       <c r="R8" t="n">
-        <v>7018955</v>
+        <v>7018927</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,12 +1350,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,22 +1375,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120304976</v>
+        <v>120304910</v>
       </c>
       <c r="B9" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1471,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483162</v>
+        <v>483054</v>
       </c>
       <c r="R9" t="n">
-        <v>7019011</v>
+        <v>7019113</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120305078</v>
+        <v>120304911</v>
       </c>
       <c r="B10" t="n">
-        <v>100269</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1577,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483060</v>
+        <v>483181</v>
       </c>
       <c r="R10" t="n">
-        <v>7019069</v>
+        <v>7019048</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,22 +1577,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120305055</v>
+        <v>120304916</v>
       </c>
       <c r="B11" t="n">
-        <v>78562</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1655,21 +1595,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1683,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483137</v>
+        <v>483185</v>
       </c>
       <c r="R11" t="n">
-        <v>7019004</v>
+        <v>7018955</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,44 +1678,39 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120304928</v>
+        <v>120305157</v>
       </c>
       <c r="B12" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1789,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483101</v>
+        <v>483163</v>
       </c>
       <c r="R12" t="n">
-        <v>7019033</v>
+        <v>7018913</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,12 +1754,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,37 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120305090</v>
+        <v>120305177</v>
       </c>
       <c r="B13" t="n">
-        <v>100269</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1895,10 +1825,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483055</v>
+        <v>483185</v>
       </c>
       <c r="R13" t="n">
-        <v>7019106</v>
+        <v>7018954</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1925,12 +1855,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,44 +1880,39 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120305013</v>
+        <v>120305419</v>
       </c>
       <c r="B14" t="n">
-        <v>98005</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2779</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2001,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483189</v>
+        <v>483178</v>
       </c>
       <c r="R14" t="n">
-        <v>7019015</v>
+        <v>7018955</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,12 +1956,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,37 +1988,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120304906</v>
+        <v>120305055</v>
       </c>
       <c r="B15" t="n">
-        <v>95553</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2107,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483141</v>
+        <v>483137</v>
       </c>
       <c r="R15" t="n">
-        <v>7019037</v>
+        <v>7019004</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2169,15 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120305096</v>
+        <v>120304976</v>
       </c>
       <c r="B16" t="n">
-        <v>56537</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2213,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483110</v>
+        <v>483162</v>
       </c>
       <c r="R16" t="n">
-        <v>7019046</v>
+        <v>7019011</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,11 +2166,6 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Läte</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2273,44 +2183,39 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120305012</v>
+        <v>120304977</v>
       </c>
       <c r="B17" t="n">
-        <v>98005</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2324,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483208</v>
+        <v>483111</v>
       </c>
       <c r="R17" t="n">
-        <v>7019003</v>
+        <v>7019035</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,15 +2291,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120304957</v>
+        <v>120304978</v>
       </c>
       <c r="B18" t="n">
-        <v>90924</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,21 +2302,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2430,10 +2330,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483132</v>
+        <v>483102</v>
       </c>
       <c r="R18" t="n">
-        <v>7018969</v>
+        <v>7019030</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,15 +2392,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120304920</v>
+        <v>120304979</v>
       </c>
       <c r="B19" t="n">
-        <v>57333</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2508,21 +2403,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2530,24 +2425,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483193</v>
+        <v>483093</v>
       </c>
       <c r="R19" t="n">
-        <v>7019005</v>
+        <v>7019013</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,15 +2493,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120304986</v>
+        <v>120304980</v>
       </c>
       <c r="B20" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2650,10 +2532,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483067</v>
+        <v>483130</v>
       </c>
       <c r="R20" t="n">
-        <v>7019094</v>
+        <v>7019014</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,15 +2594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120304911</v>
+        <v>120304986</v>
       </c>
       <c r="B21" t="n">
-        <v>90636</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,21 +2605,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2756,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483181</v>
+        <v>483067</v>
       </c>
       <c r="R21" t="n">
-        <v>7019048</v>
+        <v>7019094</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2818,37 +2695,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120304927</v>
+        <v>120304987</v>
       </c>
       <c r="B22" t="n">
-        <v>79672</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2862,10 +2734,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483071</v>
+        <v>483167</v>
       </c>
       <c r="R22" t="n">
-        <v>7019044</v>
+        <v>7019007</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2924,15 +2796,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120304916</v>
+        <v>120305317</v>
       </c>
       <c r="B23" t="n">
-        <v>90636</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2940,21 +2807,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2968,10 +2835,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483185</v>
+        <v>483152</v>
       </c>
       <c r="R23" t="n">
-        <v>7018955</v>
+        <v>7018936</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,12 +2865,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3030,37 +2897,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120304977</v>
+        <v>120304927</v>
       </c>
       <c r="B24" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3074,10 +2936,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483111</v>
+        <v>483071</v>
       </c>
       <c r="R24" t="n">
-        <v>7019035</v>
+        <v>7019044</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,37 +2998,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120305505</v>
+        <v>120304928</v>
       </c>
       <c r="B25" t="n">
-        <v>57333</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3180,10 +3037,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483156</v>
+        <v>483101</v>
       </c>
       <c r="R25" t="n">
-        <v>7018950</v>
+        <v>7019033</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3210,17 +3067,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3247,15 +3099,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120304923</v>
+        <v>120272455</v>
       </c>
       <c r="B26" t="n">
-        <v>57486</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3263,38 +3110,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kallkas, Jmt</t>
+          <t>Sveden, Sveden, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483103</v>
+        <v>483213</v>
       </c>
       <c r="R26" t="n">
-        <v>7019023</v>
+        <v>7018962</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3321,12 +3169,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3341,27 +3189,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120304980</v>
+        <v>120304920</v>
       </c>
       <c r="B27" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3369,21 +3212,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3391,16 +3234,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kallkas, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483130</v>
+        <v>483193</v>
       </c>
       <c r="R27" t="n">
-        <v>7019014</v>
+        <v>7019005</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3459,15 +3310,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120305124</v>
+        <v>120305505</v>
       </c>
       <c r="B28" t="n">
-        <v>95553</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3475,21 +3321,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3503,10 +3349,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483178</v>
+        <v>483156</v>
       </c>
       <c r="R28" t="n">
-        <v>7018954</v>
+        <v>7018950</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3541,6 +3387,11 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3562,6 +3413,1233 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120305096</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>483110</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7019046</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Läte</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120272493</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sveden, Sveden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>483195</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7018972</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120304923</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>483103</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7019023</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120305011</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>483217</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7019009</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120305012</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>483208</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7019003</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120305013</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>483189</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7019015</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120305283</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>483154</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7018948</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120305284</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>483197</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7018961</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120305285</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>483207</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7018957</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120305078</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>483060</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7019069</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson, Andrea Lindberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120305089</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>483231</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7018998</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120305090</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kallkas, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>483055</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7019106</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Andrea Lindberg, Klas Andersson, Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1959-2022 artfynd.xlsx
+++ b/artfynd/A 1959-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304905</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304906</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305124</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120420881</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304957</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305407</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120420884</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304910</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304911</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304916</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305157</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305177</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305419</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305055</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304976</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304977</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304978</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304979</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304980</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2692,6 +2792,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304986</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2793,6 +2898,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304987</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2894,6 +3004,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305317</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2995,6 +3110,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304927</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3096,6 +3216,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304928</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3198,6 +3323,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272455</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3307,6 +3437,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304920</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3413,6 +3548,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305505</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3519,6 +3659,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305096</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3630,6 +3775,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120272493</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3731,6 +3881,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120304923</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3832,6 +3987,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305011</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3933,6 +4093,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305012</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4034,6 +4199,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305013</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4135,6 +4305,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305283</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4236,6 +4411,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305284</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4337,6 +4517,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305285</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4438,6 +4623,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305078</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4539,6 +4729,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305089</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4640,8 +4835,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120305090</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>